--- a/산출물/04_3일차_팀프로젝트_실습기획서_템플렛.xlsx
+++ b/산출물/04_3일차_팀프로젝트_실습기획서_템플렛.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAFY\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAFY\Desktop\안재윤\localhub\산출물\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4523D3D7-DDCB-487B-B54F-072373AC69B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE06840-C727-44EC-BCBA-F8A8A45ACB02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_사용안내" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="251">
   <si>
     <t>실습 소재</t>
   </si>
@@ -7484,450 +7484,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>지도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시각화</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> - Kakao Maps API</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>권역</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>내</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>관광지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>맛집</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>위치를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>지도에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>마커로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>표시</t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>지도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>필터</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>기능</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>카테고리별</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>관광지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>맛집</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>마커</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>필터링</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>및</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>클릭</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>상세정보</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>팝업</t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="맑은 고딕"/>
@@ -8551,17 +8107,22 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>다크 모드</t>
-    </r>
-    <r>
-      <rPr>
+      <t>Should / Could have (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>선택</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="10"/>
         <color rgb="FF222222"/>
         <rFont val="Arial"/>
@@ -8571,422 +8132,701 @@
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지도 시각화/다크 모드</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Won't have (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이번</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> MVP </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>범위에서</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>제외</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="10"/>
         <color rgb="FF222222"/>
         <rFont val="돋움"/>
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>다크 모드 기능 추가</t>
+      <t>프론트 엔드에서 사용한 기능 선정</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
     </r>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t>Should / Could have (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>선택</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회원가입</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>로그인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>소셜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>인증, 커뮤니티 기능</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>등</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사용자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>계정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>체계</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>요구사항 분석 및 MVP 확정</t>
+  </si>
+  <si>
+    <t>화면 UI/UX 와이어프레임 설계</t>
+  </si>
+  <si>
+    <t>Vue.js 3 (Vite) 프로젝트 세팅 및 환경 구성</t>
+  </si>
+  <si>
+    <t>팀전체</t>
+  </si>
+  <si>
+    <t>FE</t>
+  </si>
+  <si>
+    <t>제공 JSON 데이터 연동 및 리스트 UI 구현</t>
+  </si>
+  <si>
+    <t>localStorage 기반 커뮤니티 게시판 CRUD 구현</t>
+  </si>
+  <si>
+    <t>OpenAI API 연동 및 챗봇 컴포넌트 개발</t>
+  </si>
+  <si>
+    <t>선택 기능(날씨 API, 게시판 검색) 구현</t>
+  </si>
+  <si>
+    <t>Netlify 환경 설정 및 빌드 배포</t>
+  </si>
+  <si>
+    <t>배포 사이트 URL 동작 확인 및 버그 수정</t>
+  </si>
+  <si>
+    <t>기능 명세서 및 데이터 라이선스 목록 작성</t>
+  </si>
+  <si>
+    <t>시연용 발표 PPT 작성 및 제출물 종합 점검</t>
+  </si>
+  <si>
+    <t>2026-07-14</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>예정</t>
+  </si>
+  <si>
+    <t>완료</t>
+  </si>
+  <si>
+    <t>제약</t>
+  </si>
+  <si>
+    <t>데이터 라이선스 준수</t>
+  </si>
+  <si>
+    <t>제공 JSON 외 추가 데이터를 수집할 경우, 반드시 해당 데이터의 사용 범위(공공누리 유형 등)를 사전 확인하여 활용 가능 여부를 검토해야 합니다.</t>
+  </si>
+  <si>
+    <t>무단 데이터 크롤링 및 사용으로 인한 법적 리스크를 원천 차단하기 위한 필수 조치입니다.</t>
+  </si>
+  <si>
+    <t>API 과금 및 보안</t>
+  </si>
+  <si>
+    <t>프론트엔드 코드에 API 키가 노출될 수 있으므로, 반드시 사용량 제한이 적용된 키를 사용하고 결제 한도를 낮게 설정해야 합니다.</t>
+  </si>
+  <si>
+    <t>브라우저에서의 키 관리는 보안 취약점이 큽니다. 개발팀에 엄격한 환경변수(.env) 통제 및 주기적인 과금 모니터링을 지시해야 합니다.</t>
+  </si>
+  <si>
+    <t>비인가 AI 도구 금지</t>
+  </si>
+  <si>
+    <t>개발 시 VSCode Copilot과 OPENAI API KEY 조합만 허용되며, Claude Code나 Cursor 등 타 AI 도구는 보안상의 이유로 사용이 불가합니다.</t>
+  </si>
+  <si>
+    <t>고객사의 보안 정책 위반 시 계약 불이익이 예상되므로, 프로젝트 투입 전 참여 인력 전원의 개발 환경 점검이 요구됩니다.</t>
+  </si>
+  <si>
+    <t>요구사항 변경 불가</t>
+  </si>
+  <si>
+    <t>유연한 일정 변경이 불가능합니다. 기획안 및 WBS 확정 단계에서 모든 예외 케이스를 도출하고 고객사의 최종 승인을 받아야 합니다.</t>
+  </si>
+  <si>
+    <t>산출물 및 납기 엄수</t>
+  </si>
+  <si>
+    <t>필수</t>
+  </si>
+  <si>
+    <t>프론트엔드 개발 환경</t>
+  </si>
+  <si>
+    <t>서버 의존성을 배제한 상태에서 데이터의 로딩 및 화면 전환 최적화에 주력해야 합니다.</t>
+  </si>
+  <si>
+    <t>익명 커뮤니티(CRUD)</t>
+  </si>
+  <si>
+    <t>AI 챗봇 탑재</t>
+  </si>
+  <si>
+    <t>AI가 제시된 JSON 데이터 범위 내에서만 정확히 답변하도록 프롬프트 체이닝 등 환각(Hallucination) 방지 로직을 세밀하게 구성해야 합니다.</t>
+  </si>
+  <si>
+    <t>지정 서비스 배포</t>
+  </si>
+  <si>
+    <t>저장소(Git) 연동형 CI/CD 파이프라인을 구축해 수정 사항이 신속하고 안정적으로 배포되도록 조치해야 합니다.</t>
+  </si>
+  <si>
+    <t>선택</t>
+  </si>
+  <si>
+    <t>부가 기능 추가</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시각화</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> - Kakao Maps API</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>권역</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>관광지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>맛집</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>위치를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지도에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마커로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>표시</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다크</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t xml:space="preserve"> - </t>
     </r>
     <r>
       <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>지도 시각화/다크 모드</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다크</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기능</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>추가</t>
     </r>
     <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Won't have (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이번</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> MVP </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>범위에서</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>제외</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> - </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>프론트 엔드에서 사용한 기능 선정</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>회원가입</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>로그인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>소셜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>인증, 커뮤니티 기능</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>등</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>사용자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>계정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>체계</t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>요구사항 분석 및 MVP 확정</t>
-  </si>
-  <si>
-    <t>화면 UI/UX 와이어프레임 설계</t>
-  </si>
-  <si>
-    <t>Vue.js 3 (Vite) 프로젝트 세팅 및 환경 구성</t>
-  </si>
-  <si>
-    <t>팀전체</t>
-  </si>
-  <si>
-    <t>FE</t>
-  </si>
-  <si>
-    <t>제공 JSON 데이터 연동 및 리스트 UI 구현</t>
-  </si>
-  <si>
-    <t>localStorage 기반 커뮤니티 게시판 CRUD 구현</t>
-  </si>
-  <si>
-    <t>OpenAI API 연동 및 챗봇 컴포넌트 개발</t>
-  </si>
-  <si>
-    <t>선택 기능(날씨 API, 게시판 검색) 구현</t>
-  </si>
-  <si>
-    <t>Netlify 환경 설정 및 빌드 배포</t>
-  </si>
-  <si>
-    <t>배포 사이트 URL 동작 확인 및 버그 수정</t>
-  </si>
-  <si>
-    <t>기능 명세서 및 데이터 라이선스 목록 작성</t>
-  </si>
-  <si>
-    <t>시연용 발표 PPT 작성 및 제출물 종합 점검</t>
-  </si>
-  <si>
-    <t>2026-07-14</t>
-  </si>
-  <si>
-    <t>2026-07-15</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>예정</t>
-  </si>
-  <si>
-    <t>완료</t>
-  </si>
-  <si>
-    <t>제약</t>
-  </si>
-  <si>
-    <t>데이터 라이선스 준수</t>
-  </si>
-  <si>
-    <t>제공 JSON 외 추가 데이터를 수집할 경우, 반드시 해당 데이터의 사용 범위(공공누리 유형 등)를 사전 확인하여 활용 가능 여부를 검토해야 합니다.</t>
-  </si>
-  <si>
-    <t>무단 데이터 크롤링 및 사용으로 인한 법적 리스크를 원천 차단하기 위한 필수 조치입니다.</t>
-  </si>
-  <si>
-    <t>API 과금 및 보안</t>
-  </si>
-  <si>
-    <t>프론트엔드 코드에 API 키가 노출될 수 있으므로, 반드시 사용량 제한이 적용된 키를 사용하고 결제 한도를 낮게 설정해야 합니다.</t>
-  </si>
-  <si>
-    <t>브라우저에서의 키 관리는 보안 취약점이 큽니다. 개발팀에 엄격한 환경변수(.env) 통제 및 주기적인 과금 모니터링을 지시해야 합니다.</t>
-  </si>
-  <si>
-    <t>비인가 AI 도구 금지</t>
-  </si>
-  <si>
-    <t>개발 시 VSCode Copilot과 OPENAI API KEY 조합만 허용되며, Claude Code나 Cursor 등 타 AI 도구는 보안상의 이유로 사용이 불가합니다.</t>
-  </si>
-  <si>
-    <t>고객사의 보안 정책 위반 시 계약 불이익이 예상되므로, 프로젝트 투입 전 참여 인력 전원의 개발 환경 점검이 요구됩니다.</t>
-  </si>
-  <si>
-    <t>요구사항 변경 불가</t>
-  </si>
-  <si>
-    <t>유연한 일정 변경이 불가능합니다. 기획안 및 WBS 확정 단계에서 모든 예외 케이스를 도출하고 고객사의 최종 승인을 받아야 합니다.</t>
-  </si>
-  <si>
-    <t>산출물 및 납기 엄수</t>
-  </si>
-  <si>
-    <t>필수</t>
-  </si>
-  <si>
-    <t>프론트엔드 개발 환경</t>
-  </si>
-  <si>
-    <t>서버 의존성을 배제한 상태에서 데이터의 로딩 및 화면 전환 최적화에 주력해야 합니다.</t>
-  </si>
-  <si>
-    <t>익명 커뮤니티(CRUD)</t>
-  </si>
-  <si>
-    <t>AI 챗봇 탑재</t>
-  </si>
-  <si>
-    <t>AI가 제시된 JSON 데이터 범위 내에서만 정확히 답변하도록 프롬프트 체이닝 등 환각(Hallucination) 방지 로직을 세밀하게 구성해야 합니다.</t>
-  </si>
-  <si>
-    <t>지정 서비스 배포</t>
-  </si>
-  <si>
-    <t>저장소(Git) 연동형 CI/CD 파이프라인을 구축해 수정 사항이 신속하고 안정적으로 배포되도록 조치해야 합니다.</t>
-  </si>
-  <si>
-    <t>선택</t>
-  </si>
-  <si>
-    <t>부가 기능 추가</t>
   </si>
 </sst>
 </file>
@@ -9297,13 +9137,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF222222"/>
-      <name val="돋움"/>
-      <family val="2"/>
-      <charset val="129"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF222222"/>
@@ -9341,6 +9174,12 @@
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF222222"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="21">
@@ -9465,7 +9304,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -9607,12 +9446,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -9692,6 +9540,64 @@
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="18" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="19" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="20" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -9738,13 +9644,13 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -9759,29 +9665,14 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -9819,71 +9710,35 @@
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="18" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="19" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="20" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -10201,10 +10056,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="31.5" customHeight="1">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="55" t="s">
         <v>108</v>
       </c>
-      <c r="C2" s="35"/>
+      <c r="C2" s="55"/>
     </row>
     <row r="4" spans="2:3" ht="19.5" customHeight="1">
       <c r="B4" s="14" t="s">
@@ -10239,10 +10094,10 @@
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="51" t="s">
         <v>114</v>
       </c>
-      <c r="C9" s="32"/>
+      <c r="C9" s="52"/>
     </row>
     <row r="10" spans="2:3" ht="27">
       <c r="B10" s="4" t="s">
@@ -10293,28 +10148,28 @@
       </c>
     </row>
     <row r="17" spans="2:3" ht="15" customHeight="1">
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="34"/>
+      <c r="C17" s="54"/>
     </row>
     <row r="18" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B18" s="36" t="s">
+      <c r="B18" s="56" t="s">
         <v>125</v>
       </c>
-      <c r="C18" s="37"/>
+      <c r="C18" s="57"/>
     </row>
     <row r="19" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B19" s="29" t="s">
+      <c r="B19" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="30"/>
+      <c r="C19" s="50"/>
     </row>
     <row r="20" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B20" s="29" t="s">
+      <c r="B20" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="30"/>
+      <c r="C20" s="50"/>
     </row>
     <row r="21" spans="2:3" ht="27.75" customHeight="1"/>
   </sheetData>
@@ -10348,13 +10203,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="30" customHeight="1">
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
     </row>
     <row r="4" spans="2:10" ht="19.5" customHeight="1">
       <c r="B4" s="6" t="s">
@@ -10446,46 +10301,46 @@
     </row>
     <row r="9" spans="2:10" ht="14.1" customHeight="1"/>
     <row r="10" spans="2:10" ht="15" customHeight="1">
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="62" t="s">
         <v>126</v>
       </c>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="32"/>
+      <c r="C10" s="59"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="52"/>
     </row>
     <row r="11" spans="2:10" ht="24" customHeight="1">
       <c r="B11" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="38" t="s">
+      <c r="C11" s="58" t="s">
         <v>127</v>
       </c>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
     </row>
     <row r="12" spans="2:10" ht="24" customHeight="1">
       <c r="B12" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="38" t="s">
+      <c r="C12" s="58" t="s">
         <v>128</v>
       </c>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
     </row>
     <row r="13" spans="2:10" ht="24" customHeight="1">
       <c r="B13" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="38" t="s">
+      <c r="C13" s="58" t="s">
         <v>129</v>
       </c>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -10514,10 +10369,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="31.5" customHeight="1">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="55" t="s">
         <v>108</v>
       </c>
-      <c r="C2" s="35"/>
+      <c r="C2" s="55"/>
     </row>
     <row r="4" spans="2:3" ht="19.5" customHeight="1">
       <c r="B4" s="14" t="s">
@@ -10552,10 +10407,10 @@
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="51" t="s">
         <v>114</v>
       </c>
-      <c r="C9" s="32"/>
+      <c r="C9" s="52"/>
     </row>
     <row r="10" spans="2:3" ht="27">
       <c r="B10" s="4" t="s">
@@ -10606,38 +10461,38 @@
       </c>
     </row>
     <row r="17" spans="2:3" ht="15" customHeight="1">
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="34"/>
+      <c r="C17" s="54"/>
     </row>
     <row r="18" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B18" s="36" t="s">
+      <c r="B18" s="56" t="s">
         <v>125</v>
       </c>
-      <c r="C18" s="37"/>
+      <c r="C18" s="57"/>
     </row>
     <row r="19" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B19" s="29" t="s">
+      <c r="B19" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="30"/>
+      <c r="C19" s="50"/>
     </row>
     <row r="20" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B20" s="29" t="s">
+      <c r="B20" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="30"/>
+      <c r="C20" s="50"/>
     </row>
     <row r="21" spans="2:3" ht="27.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="B20:C20"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -10662,22 +10517,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="30" customHeight="1">
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
     </row>
     <row r="3" spans="2:6" ht="28.35" customHeight="1">
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="64" t="s">
         <v>138</v>
       </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="32"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="52"/>
     </row>
     <row r="4" spans="2:6" ht="35.65" customHeight="1">
       <c r="B4" s="8" t="s">
@@ -10706,172 +10561,172 @@
       <c r="F5" s="9"/>
     </row>
     <row r="6" spans="2:6" ht="30" customHeight="1">
-      <c r="B6" s="91" t="s">
+      <c r="B6" s="44" t="s">
+        <v>226</v>
+      </c>
+      <c r="C6" s="45" t="s">
+        <v>227</v>
+      </c>
+      <c r="D6" s="46" t="s">
+        <v>228</v>
+      </c>
+      <c r="E6" s="45" t="s">
+        <v>148</v>
+      </c>
+      <c r="F6" s="46" t="s">
         <v>229</v>
       </c>
-      <c r="C6" s="92" t="s">
+    </row>
+    <row r="7" spans="2:6" ht="30" customHeight="1">
+      <c r="B7" s="44" t="s">
+        <v>226</v>
+      </c>
+      <c r="C7" s="45" t="s">
         <v>230</v>
       </c>
-      <c r="D6" s="93" t="s">
+      <c r="D7" s="46" t="s">
         <v>231</v>
       </c>
-      <c r="E6" s="92" t="s">
-        <v>148</v>
-      </c>
-      <c r="F6" s="93" t="s">
+      <c r="E7" s="45" t="s">
+        <v>149</v>
+      </c>
+      <c r="F7" s="46" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="30" customHeight="1">
-      <c r="B7" s="91" t="s">
-        <v>229</v>
-      </c>
-      <c r="C7" s="92" t="s">
+    <row r="8" spans="2:6" ht="30" customHeight="1">
+      <c r="B8" s="44" t="s">
+        <v>226</v>
+      </c>
+      <c r="C8" s="45" t="s">
         <v>233</v>
       </c>
-      <c r="D7" s="93" t="s">
+      <c r="D8" s="46" t="s">
         <v>234</v>
       </c>
-      <c r="E7" s="92" t="s">
-        <v>149</v>
-      </c>
-      <c r="F7" s="93" t="s">
+      <c r="E8" s="45" t="s">
+        <v>150</v>
+      </c>
+      <c r="F8" s="46" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="8" spans="2:6" ht="30" customHeight="1">
-      <c r="B8" s="91" t="s">
-        <v>229</v>
-      </c>
-      <c r="C8" s="92" t="s">
+    <row r="9" spans="2:6" ht="30" customHeight="1">
+      <c r="B9" s="44" t="s">
+        <v>226</v>
+      </c>
+      <c r="C9" s="45" t="s">
         <v>236</v>
       </c>
-      <c r="D8" s="93" t="s">
+      <c r="D9" s="46" t="s">
+        <v>151</v>
+      </c>
+      <c r="E9" s="45" t="s">
+        <v>152</v>
+      </c>
+      <c r="F9" s="46" t="s">
         <v>237</v>
       </c>
-      <c r="E8" s="92" t="s">
-        <v>150</v>
-      </c>
-      <c r="F8" s="93" t="s">
+    </row>
+    <row r="10" spans="2:6" ht="30" customHeight="1">
+      <c r="B10" s="44" t="s">
+        <v>226</v>
+      </c>
+      <c r="C10" s="45" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="9" spans="2:6" ht="30" customHeight="1">
-      <c r="B9" s="91" t="s">
-        <v>229</v>
-      </c>
-      <c r="C9" s="92" t="s">
+      <c r="D10" s="46" t="s">
+        <v>153</v>
+      </c>
+      <c r="E10" s="45" t="s">
+        <v>154</v>
+      </c>
+      <c r="F10" s="46" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" ht="30" customHeight="1">
+      <c r="B11" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="D9" s="93" t="s">
-        <v>151</v>
-      </c>
-      <c r="E9" s="92" t="s">
-        <v>152</v>
-      </c>
-      <c r="F9" s="93" t="s">
+      <c r="C11" s="45" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="10" spans="2:6" ht="30" customHeight="1">
-      <c r="B10" s="91" t="s">
-        <v>229</v>
-      </c>
-      <c r="C10" s="92" t="s">
+      <c r="D11" s="46" t="s">
+        <v>156</v>
+      </c>
+      <c r="E11" s="45" t="s">
+        <v>157</v>
+      </c>
+      <c r="F11" s="46" t="s">
         <v>241</v>
       </c>
-      <c r="D10" s="93" t="s">
-        <v>153</v>
-      </c>
-      <c r="E10" s="92" t="s">
-        <v>154</v>
-      </c>
-      <c r="F10" s="93" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" ht="30" customHeight="1">
-      <c r="B11" s="94" t="s">
+    </row>
+    <row r="12" spans="2:6" ht="30" customHeight="1">
+      <c r="B12" s="47" t="s">
+        <v>239</v>
+      </c>
+      <c r="C12" s="45" t="s">
         <v>242</v>
       </c>
-      <c r="C11" s="92" t="s">
+      <c r="D12" s="46" t="s">
+        <v>158</v>
+      </c>
+      <c r="E12" s="45" t="s">
+        <v>159</v>
+      </c>
+      <c r="F12" s="46" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" ht="30" customHeight="1">
+      <c r="B13" s="47" t="s">
+        <v>239</v>
+      </c>
+      <c r="C13" s="45" t="s">
         <v>243</v>
       </c>
-      <c r="D11" s="93" t="s">
-        <v>156</v>
-      </c>
-      <c r="E11" s="92" t="s">
-        <v>157</v>
-      </c>
-      <c r="F11" s="93" t="s">
+      <c r="D13" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="E13" s="45" t="s">
+        <v>162</v>
+      </c>
+      <c r="F13" s="46" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="30" customHeight="1">
-      <c r="B12" s="94" t="s">
-        <v>242</v>
-      </c>
-      <c r="C12" s="92" t="s">
+    <row r="14" spans="2:6" ht="30" customHeight="1">
+      <c r="B14" s="47" t="s">
+        <v>239</v>
+      </c>
+      <c r="C14" s="45" t="s">
         <v>245</v>
       </c>
-      <c r="D12" s="93" t="s">
-        <v>158</v>
-      </c>
-      <c r="E12" s="92" t="s">
-        <v>159</v>
-      </c>
-      <c r="F12" s="93" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6" ht="30" customHeight="1">
-      <c r="B13" s="94" t="s">
-        <v>242</v>
-      </c>
-      <c r="C13" s="92" t="s">
+      <c r="D14" s="46" t="s">
+        <v>163</v>
+      </c>
+      <c r="E14" s="45" t="s">
+        <v>164</v>
+      </c>
+      <c r="F14" s="46" t="s">
         <v>246</v>
       </c>
-      <c r="D13" s="93" t="s">
-        <v>161</v>
-      </c>
-      <c r="E13" s="92" t="s">
-        <v>162</v>
-      </c>
-      <c r="F13" s="93" t="s">
+    </row>
+    <row r="15" spans="2:6" ht="30" customHeight="1">
+      <c r="B15" s="48" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="14" spans="2:6" ht="30" customHeight="1">
-      <c r="B14" s="94" t="s">
-        <v>242</v>
-      </c>
-      <c r="C14" s="92" t="s">
+      <c r="C15" s="45" t="s">
         <v>248</v>
       </c>
-      <c r="D14" s="93" t="s">
-        <v>163</v>
-      </c>
-      <c r="E14" s="92" t="s">
-        <v>164</v>
-      </c>
-      <c r="F14" s="93" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6" ht="30" customHeight="1">
-      <c r="B15" s="95" t="s">
-        <v>250</v>
-      </c>
-      <c r="C15" s="92" t="s">
-        <v>251</v>
-      </c>
-      <c r="D15" s="93" t="s">
+      <c r="D15" s="46" t="s">
         <v>165</v>
       </c>
-      <c r="E15" s="92" t="s">
+      <c r="E15" s="45" t="s">
         <v>166</v>
       </c>
-      <c r="F15" s="93" t="s">
+      <c r="F15" s="46" t="s">
         <v>167</v>
       </c>
     </row>
@@ -10965,37 +10820,37 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="30" customHeight="1">
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
     </row>
     <row r="3" spans="2:8" ht="72.400000000000006" customHeight="1">
-      <c r="B3" s="45" t="s">
+      <c r="B3" s="65" t="s">
         <v>132</v>
       </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="32"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="52"/>
     </row>
     <row r="4" spans="2:8" ht="18" customHeight="1">
-      <c r="B4" s="46" t="s">
+      <c r="B4" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="32"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="52"/>
     </row>
     <row r="5" spans="2:8" ht="31.5" customHeight="1">
       <c r="B5" s="10" t="s">
@@ -11189,98 +11044,98 @@
       </c>
     </row>
     <row r="13" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B13" s="74" t="s">
+      <c r="B13" s="30" t="s">
         <v>181</v>
       </c>
-      <c r="C13" s="75" t="s">
+      <c r="C13" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="D13" s="76">
+      <c r="D13" s="32">
         <v>2</v>
       </c>
-      <c r="E13" s="76">
+      <c r="E13" s="32">
         <v>4</v>
       </c>
-      <c r="F13" s="76">
+      <c r="F13" s="32">
         <v>3</v>
       </c>
-      <c r="G13" s="76">
+      <c r="G13" s="32">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="H13" s="76" t="s">
+      <c r="H13" s="32" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="14" spans="2:8" ht="28.5" customHeight="1">
-      <c r="B14" s="78" t="s">
+      <c r="B14" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="C14" s="75" t="s">
+      <c r="C14" s="31" t="s">
         <v>184</v>
       </c>
-      <c r="D14" s="76">
+      <c r="D14" s="32">
         <v>1</v>
       </c>
-      <c r="E14" s="76">
+      <c r="E14" s="32">
         <v>5</v>
       </c>
-      <c r="F14" s="76">
+      <c r="F14" s="32">
         <v>4</v>
       </c>
-      <c r="G14" s="76">
+      <c r="G14" s="32">
         <f t="shared" ref="G14:G15" si="1">IF(OR(E14="",F14=""),"",E14*F14*2)</f>
         <v>40</v>
       </c>
-      <c r="H14" s="76" t="s">
+      <c r="H14" s="32" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="47.25" customHeight="1">
-      <c r="B15" s="79" t="s">
+      <c r="B15" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="C15" s="80" t="s">
+      <c r="C15" s="36" t="s">
         <v>186</v>
       </c>
-      <c r="D15" s="77">
+      <c r="D15" s="33">
         <v>1</v>
       </c>
-      <c r="E15" s="77">
+      <c r="E15" s="33">
         <v>5</v>
       </c>
-      <c r="F15" s="77">
+      <c r="F15" s="33">
         <v>3</v>
       </c>
-      <c r="G15" s="77">
+      <c r="G15" s="33">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="H15" s="77" t="s">
+      <c r="H15" s="33" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="16" spans="2:8" ht="27">
-      <c r="B16" s="81" t="s">
+      <c r="B16" s="37" t="s">
         <v>187</v>
       </c>
-      <c r="C16" s="83" t="s">
+      <c r="C16" s="39" t="s">
         <v>188</v>
       </c>
-      <c r="D16" s="82">
+      <c r="D16" s="38">
         <v>2</v>
       </c>
-      <c r="E16" s="82">
+      <c r="E16" s="38">
         <v>4</v>
       </c>
-      <c r="F16" s="82">
+      <c r="F16" s="38">
         <v>4</v>
       </c>
-      <c r="G16" s="82">
+      <c r="G16" s="38">
         <f t="shared" ref="G16" si="2">IF(OR(E16="",F16=""),"",E16*F16*2)</f>
         <v>32</v>
       </c>
-      <c r="H16" s="82" t="s">
+      <c r="H16" s="38" t="s">
         <v>190</v>
       </c>
     </row>
@@ -11288,14 +11143,14 @@
       <c r="B18" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="C18" s="84" t="s">
-        <v>204</v>
-      </c>
-      <c r="D18" s="85"/>
-      <c r="E18" s="85"/>
-      <c r="F18" s="85"/>
-      <c r="G18" s="85"/>
-      <c r="H18" s="86"/>
+      <c r="C18" s="67" t="s">
+        <v>202</v>
+      </c>
+      <c r="D18" s="68"/>
+      <c r="E18" s="68"/>
+      <c r="F18" s="68"/>
+      <c r="G18" s="68"/>
+      <c r="H18" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -11345,7 +11200,7 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="B2:C24"/>
+  <dimension ref="B2:C23"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -11355,16 +11210,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1">
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="41"/>
+      <c r="C2" s="61"/>
     </row>
     <row r="3" spans="2:3" ht="18" customHeight="1">
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="76" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="32"/>
+      <c r="C3" s="52"/>
     </row>
     <row r="4" spans="2:3" ht="30" customHeight="1">
       <c r="B4" s="1" t="s">
@@ -11379,7 +11234,7 @@
         <v>45</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="30" customHeight="1">
@@ -11395,111 +11250,108 @@
         <v>47</v>
       </c>
       <c r="C7" s="15" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="15" customHeight="1">
+      <c r="B9" s="74" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="75"/>
+    </row>
+    <row r="10" spans="2:3" ht="25.5" customHeight="1">
+      <c r="B10" s="49" t="s">
+        <v>195</v>
+      </c>
+      <c r="C10" s="50"/>
+    </row>
+    <row r="11" spans="2:3" ht="25.5" customHeight="1">
+      <c r="B11" s="49" t="s">
+        <v>196</v>
+      </c>
+      <c r="C11" s="50"/>
+    </row>
+    <row r="12" spans="2:3" ht="25.5" customHeight="1">
+      <c r="B12" s="56" t="s">
+        <v>197</v>
+      </c>
+      <c r="C12" s="57"/>
+    </row>
+    <row r="13" spans="2:3" ht="25.5" customHeight="1">
+      <c r="B13" s="56" t="s">
+        <v>198</v>
+      </c>
+      <c r="C13" s="57"/>
+    </row>
+    <row r="14" spans="2:3" ht="25.5" customHeight="1">
+      <c r="B14" s="49" t="s">
+        <v>199</v>
+      </c>
+      <c r="C14" s="50"/>
+    </row>
+    <row r="15" spans="2:3">
+      <c r="B15" s="58" t="s">
+        <v>249</v>
+      </c>
+      <c r="C15" s="50"/>
+    </row>
+    <row r="16" spans="2:3" s="29" customFormat="1">
+      <c r="B16" s="97"/>
+      <c r="C16" s="98"/>
+    </row>
+    <row r="17" spans="2:3" ht="15" customHeight="1">
+      <c r="B17" s="72" t="s">
+        <v>205</v>
+      </c>
+      <c r="C17" s="73"/>
+    </row>
+    <row r="18" spans="2:3" ht="25.5" customHeight="1">
+      <c r="B18" s="58" t="s">
+        <v>250</v>
+      </c>
+      <c r="C18" s="50"/>
+    </row>
+    <row r="20" spans="2:3" ht="15" customHeight="1">
+      <c r="B20" s="70" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="47" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="48"/>
-    </row>
-    <row r="10" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B10" s="29" t="s">
-        <v>195</v>
-      </c>
-      <c r="C10" s="30"/>
-    </row>
-    <row r="11" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B11" s="29" t="s">
-        <v>196</v>
-      </c>
-      <c r="C11" s="30"/>
-    </row>
-    <row r="12" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B12" s="36" t="s">
-        <v>197</v>
-      </c>
-      <c r="C12" s="37"/>
-    </row>
-    <row r="13" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B13" s="36" t="s">
-        <v>198</v>
-      </c>
-      <c r="C13" s="37"/>
-    </row>
-    <row r="14" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B14" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="C14" s="30"/>
-    </row>
-    <row r="16" spans="2:3" ht="15" customHeight="1">
-      <c r="B16" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="C16" s="53"/>
-    </row>
-    <row r="17" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B17" s="38" t="s">
-        <v>202</v>
-      </c>
-      <c r="C17" s="30"/>
-    </row>
-    <row r="18" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B18" s="38" t="s">
-        <v>203</v>
-      </c>
-      <c r="C18" s="30"/>
-    </row>
-    <row r="19" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B19" s="38" t="s">
+      <c r="C20" s="71"/>
+    </row>
+    <row r="21" spans="2:3" ht="25.5" customHeight="1">
+      <c r="B21" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="C19" s="30"/>
-    </row>
-    <row r="21" spans="2:3" ht="15" customHeight="1">
-      <c r="B21" s="50" t="s">
-        <v>209</v>
-      </c>
-      <c r="C21" s="51"/>
+      <c r="C21" s="50"/>
     </row>
     <row r="22" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B22" s="38" t="s">
-        <v>210</v>
-      </c>
-      <c r="C22" s="30"/>
+      <c r="B22" s="49" t="s">
+        <v>200</v>
+      </c>
+      <c r="C22" s="50"/>
     </row>
     <row r="23" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B23" s="29" t="s">
-        <v>200</v>
-      </c>
-      <c r="C23" s="30"/>
-    </row>
-    <row r="24" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B24" s="38" t="s">
+      <c r="B23" s="58" t="s">
         <v>201</v>
       </c>
-      <c r="C24" s="30"/>
+      <c r="C23" s="50"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
+  <mergeCells count="15">
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B9:C9"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B17:C17"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -11530,36 +11382,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="27.75" customHeight="1">
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="90" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="61"/>
+      <c r="M2" s="61"/>
     </row>
     <row r="3" spans="2:13" ht="79.7" customHeight="1">
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="89" t="s">
         <v>133</v>
       </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="32"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="59"/>
+      <c r="L3" s="59"/>
+      <c r="M3" s="52"/>
     </row>
     <row r="4" spans="2:13" ht="25.5" customHeight="1">
       <c r="B4" s="13" t="s">
@@ -11603,20 +11455,20 @@
       <c r="B5" s="5">
         <v>1</v>
       </c>
-      <c r="C5" s="87" t="s">
+      <c r="C5" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="D5" s="88" t="s">
+      <c r="D5" s="41" t="s">
+        <v>208</v>
+      </c>
+      <c r="E5" s="40" t="s">
         <v>211</v>
       </c>
-      <c r="E5" s="87" t="s">
-        <v>214</v>
-      </c>
-      <c r="F5" s="90" t="s">
-        <v>224</v>
-      </c>
-      <c r="G5" s="90" t="s">
-        <v>224</v>
+      <c r="F5" s="43" t="s">
+        <v>221</v>
+      </c>
+      <c r="G5" s="43" t="s">
+        <v>221</v>
       </c>
       <c r="H5" s="5">
         <f t="shared" ref="H5:H18" si="0">IF(OR(F5="",G5=""),"",G5-F5+1)</f>
@@ -11626,9 +11478,9 @@
         <v>100</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="K5" s="89"/>
+        <v>225</v>
+      </c>
+      <c r="K5" s="42"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
     </row>
@@ -11636,20 +11488,20 @@
       <c r="B6" s="5">
         <v>2</v>
       </c>
-      <c r="C6" s="87" t="s">
+      <c r="C6" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="88" t="s">
+      <c r="D6" s="41" t="s">
+        <v>209</v>
+      </c>
+      <c r="E6" s="40" t="s">
         <v>212</v>
       </c>
-      <c r="E6" s="87" t="s">
-        <v>215</v>
-      </c>
-      <c r="F6" s="90" t="s">
-        <v>224</v>
-      </c>
-      <c r="G6" s="90" t="s">
-        <v>224</v>
+      <c r="F6" s="43" t="s">
+        <v>221</v>
+      </c>
+      <c r="G6" s="43" t="s">
+        <v>221</v>
       </c>
       <c r="H6" s="5">
         <f t="shared" si="0"/>
@@ -11659,9 +11511,9 @@
         <v>0</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="K6" s="89"/>
+        <v>224</v>
+      </c>
+      <c r="K6" s="42"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
     </row>
@@ -11669,20 +11521,20 @@
       <c r="B7" s="5">
         <v>3</v>
       </c>
-      <c r="C7" s="87" t="s">
+      <c r="C7" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="D7" s="88" t="s">
-        <v>213</v>
-      </c>
-      <c r="E7" s="87" t="s">
-        <v>215</v>
-      </c>
-      <c r="F7" s="90" t="s">
-        <v>224</v>
-      </c>
-      <c r="G7" s="90" t="s">
-        <v>224</v>
+      <c r="D7" s="41" t="s">
+        <v>210</v>
+      </c>
+      <c r="E7" s="40" t="s">
+        <v>212</v>
+      </c>
+      <c r="F7" s="43" t="s">
+        <v>221</v>
+      </c>
+      <c r="G7" s="43" t="s">
+        <v>221</v>
       </c>
       <c r="H7" s="5">
         <f t="shared" si="0"/>
@@ -11692,9 +11544,9 @@
         <v>0</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="K7" s="89"/>
+        <v>224</v>
+      </c>
+      <c r="K7" s="42"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
     </row>
@@ -11702,20 +11554,20 @@
       <c r="B8" s="5">
         <v>4</v>
       </c>
-      <c r="C8" s="87" t="s">
+      <c r="C8" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="D8" s="88" t="s">
-        <v>216</v>
-      </c>
-      <c r="E8" s="87" t="s">
-        <v>215</v>
-      </c>
-      <c r="F8" s="90" t="s">
-        <v>224</v>
-      </c>
-      <c r="G8" s="90" t="s">
-        <v>225</v>
+      <c r="D8" s="41" t="s">
+        <v>213</v>
+      </c>
+      <c r="E8" s="40" t="s">
+        <v>212</v>
+      </c>
+      <c r="F8" s="43" t="s">
+        <v>221</v>
+      </c>
+      <c r="G8" s="43" t="s">
+        <v>222</v>
       </c>
       <c r="H8" s="5">
         <f t="shared" si="0"/>
@@ -11725,30 +11577,30 @@
         <v>0</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="K8" s="89"/>
-      <c r="L8" s="89"/>
+        <v>224</v>
+      </c>
+      <c r="K8" s="42"/>
+      <c r="L8" s="42"/>
       <c r="M8" s="3"/>
     </row>
     <row r="9" spans="2:13" ht="30" customHeight="1">
       <c r="B9" s="5">
         <v>5</v>
       </c>
-      <c r="C9" s="87" t="s">
+      <c r="C9" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="D9" s="88" t="s">
-        <v>217</v>
-      </c>
-      <c r="E9" s="87" t="s">
-        <v>215</v>
-      </c>
-      <c r="F9" s="90" t="s">
-        <v>224</v>
-      </c>
-      <c r="G9" s="90" t="s">
-        <v>225</v>
+      <c r="D9" s="41" t="s">
+        <v>214</v>
+      </c>
+      <c r="E9" s="40" t="s">
+        <v>212</v>
+      </c>
+      <c r="F9" s="43" t="s">
+        <v>221</v>
+      </c>
+      <c r="G9" s="43" t="s">
+        <v>222</v>
       </c>
       <c r="H9" s="5">
         <f t="shared" si="0"/>
@@ -11758,30 +11610,30 @@
         <v>0</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="K9" s="89"/>
-      <c r="L9" s="89"/>
+        <v>224</v>
+      </c>
+      <c r="K9" s="42"/>
+      <c r="L9" s="42"/>
       <c r="M9" s="3"/>
     </row>
     <row r="10" spans="2:13" ht="30" customHeight="1">
       <c r="B10" s="5">
         <v>6</v>
       </c>
-      <c r="C10" s="87" t="s">
+      <c r="C10" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="D10" s="88" t="s">
-        <v>218</v>
-      </c>
-      <c r="E10" s="87" t="s">
+      <c r="D10" s="41" t="s">
         <v>215</v>
       </c>
-      <c r="F10" s="90" t="s">
-        <v>225</v>
-      </c>
-      <c r="G10" s="90" t="s">
-        <v>225</v>
+      <c r="E10" s="40" t="s">
+        <v>212</v>
+      </c>
+      <c r="F10" s="43" t="s">
+        <v>222</v>
+      </c>
+      <c r="G10" s="43" t="s">
+        <v>222</v>
       </c>
       <c r="H10" s="5">
         <f t="shared" si="0"/>
@@ -11791,30 +11643,30 @@
         <v>0</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K10" s="3"/>
-      <c r="L10" s="89"/>
+      <c r="L10" s="42"/>
       <c r="M10" s="3"/>
     </row>
     <row r="11" spans="2:13" ht="30" customHeight="1">
       <c r="B11" s="5">
         <v>7</v>
       </c>
-      <c r="C11" s="87" t="s">
+      <c r="C11" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="88" t="s">
-        <v>219</v>
-      </c>
-      <c r="E11" s="87" t="s">
-        <v>215</v>
-      </c>
-      <c r="F11" s="90" t="s">
-        <v>225</v>
-      </c>
-      <c r="G11" s="90" t="s">
-        <v>225</v>
+      <c r="D11" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="E11" s="40" t="s">
+        <v>212</v>
+      </c>
+      <c r="F11" s="43" t="s">
+        <v>222</v>
+      </c>
+      <c r="G11" s="43" t="s">
+        <v>222</v>
       </c>
       <c r="H11" s="5">
         <f t="shared" si="0"/>
@@ -11824,30 +11676,30 @@
         <v>0</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K11" s="3"/>
-      <c r="L11" s="89"/>
+      <c r="L11" s="42"/>
       <c r="M11" s="3"/>
     </row>
     <row r="12" spans="2:13" ht="30" customHeight="1">
       <c r="B12" s="5">
         <v>8</v>
       </c>
-      <c r="C12" s="87" t="s">
+      <c r="C12" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="88" t="s">
-        <v>220</v>
-      </c>
-      <c r="E12" s="87" t="s">
-        <v>215</v>
-      </c>
-      <c r="F12" s="90" t="s">
-        <v>225</v>
-      </c>
-      <c r="G12" s="90" t="s">
-        <v>225</v>
+      <c r="D12" s="41" t="s">
+        <v>217</v>
+      </c>
+      <c r="E12" s="40" t="s">
+        <v>212</v>
+      </c>
+      <c r="F12" s="43" t="s">
+        <v>222</v>
+      </c>
+      <c r="G12" s="43" t="s">
+        <v>222</v>
       </c>
       <c r="H12" s="5">
         <f t="shared" si="0"/>
@@ -11857,30 +11709,30 @@
         <v>0</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K12" s="3"/>
-      <c r="L12" s="89"/>
+      <c r="L12" s="42"/>
       <c r="M12" s="3"/>
     </row>
     <row r="13" spans="2:13" ht="30" customHeight="1">
       <c r="B13" s="5">
         <v>9</v>
       </c>
-      <c r="C13" s="87" t="s">
+      <c r="C13" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="D13" s="88" t="s">
-        <v>221</v>
-      </c>
-      <c r="E13" s="87" t="s">
-        <v>214</v>
-      </c>
-      <c r="F13" s="90" t="s">
-        <v>226</v>
-      </c>
-      <c r="G13" s="90" t="s">
-        <v>226</v>
+      <c r="D13" s="41" t="s">
+        <v>218</v>
+      </c>
+      <c r="E13" s="40" t="s">
+        <v>211</v>
+      </c>
+      <c r="F13" s="43" t="s">
+        <v>223</v>
+      </c>
+      <c r="G13" s="43" t="s">
+        <v>223</v>
       </c>
       <c r="H13" s="5">
         <f t="shared" si="0"/>
@@ -11890,30 +11742,30 @@
         <v>0</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
-      <c r="M13" s="89"/>
+      <c r="M13" s="42"/>
     </row>
     <row r="14" spans="2:13" ht="30" customHeight="1">
       <c r="B14" s="5">
         <v>10</v>
       </c>
-      <c r="C14" s="87" t="s">
+      <c r="C14" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="D14" s="88" t="s">
-        <v>222</v>
-      </c>
-      <c r="E14" s="87" t="s">
-        <v>214</v>
-      </c>
-      <c r="F14" s="90" t="s">
-        <v>226</v>
-      </c>
-      <c r="G14" s="90" t="s">
-        <v>226</v>
+      <c r="D14" s="41" t="s">
+        <v>219</v>
+      </c>
+      <c r="E14" s="40" t="s">
+        <v>211</v>
+      </c>
+      <c r="F14" s="43" t="s">
+        <v>223</v>
+      </c>
+      <c r="G14" s="43" t="s">
+        <v>223</v>
       </c>
       <c r="H14" s="5">
         <f t="shared" si="0"/>
@@ -11923,30 +11775,30 @@
         <v>0</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
-      <c r="M14" s="89"/>
+      <c r="M14" s="42"/>
     </row>
     <row r="15" spans="2:13" ht="30" customHeight="1">
       <c r="B15" s="5">
         <v>11</v>
       </c>
-      <c r="C15" s="87" t="s">
+      <c r="C15" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="D15" s="88" t="s">
+      <c r="D15" s="41" t="s">
+        <v>220</v>
+      </c>
+      <c r="E15" s="40" t="s">
+        <v>211</v>
+      </c>
+      <c r="F15" s="43" t="s">
         <v>223</v>
       </c>
-      <c r="E15" s="87" t="s">
-        <v>214</v>
-      </c>
-      <c r="F15" s="90" t="s">
-        <v>226</v>
-      </c>
-      <c r="G15" s="90" t="s">
-        <v>226</v>
+      <c r="G15" s="43" t="s">
+        <v>223</v>
       </c>
       <c r="H15" s="5">
         <f t="shared" si="0"/>
@@ -11956,11 +11808,11 @@
         <v>0</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
-      <c r="M15" s="89"/>
+      <c r="M15" s="42"/>
     </row>
     <row r="16" spans="2:13" ht="30" customHeight="1">
       <c r="B16" s="5">
@@ -12020,72 +11872,72 @@
       <c r="M18" s="3"/>
     </row>
     <row r="20" spans="2:13" ht="15" customHeight="1">
-      <c r="B20" s="56" t="s">
+      <c r="B20" s="91" t="s">
         <v>134</v>
       </c>
-      <c r="C20" s="57"/>
+      <c r="C20" s="92"/>
     </row>
     <row r="21" spans="2:13" ht="15" customHeight="1">
-      <c r="B21" s="58" t="s">
+      <c r="B21" s="93" t="s">
         <v>56</v>
       </c>
-      <c r="C21" s="59"/>
+      <c r="C21" s="94"/>
     </row>
     <row r="22" spans="2:13" ht="15" customHeight="1">
-      <c r="B22" s="60" t="s">
+      <c r="B22" s="95" t="s">
         <v>57</v>
       </c>
-      <c r="C22" s="61"/>
+      <c r="C22" s="96"/>
     </row>
     <row r="23" spans="2:13" ht="15" customHeight="1">
-      <c r="B23" s="64" t="s">
+      <c r="B23" s="79" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="65"/>
+      <c r="C23" s="80"/>
     </row>
     <row r="24" spans="2:13" ht="15" customHeight="1">
-      <c r="B24" s="66" t="s">
+      <c r="B24" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="C24" s="67"/>
+      <c r="C24" s="82"/>
     </row>
     <row r="25" spans="2:13" ht="15" customHeight="1">
-      <c r="B25" s="68" t="s">
+      <c r="B25" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="C25" s="69"/>
+      <c r="C25" s="84"/>
     </row>
     <row r="26" spans="2:13" ht="15" customHeight="1">
-      <c r="B26" s="70" t="s">
+      <c r="B26" s="85" t="s">
         <v>61</v>
       </c>
-      <c r="C26" s="71"/>
+      <c r="C26" s="86"/>
     </row>
     <row r="27" spans="2:13" ht="15" customHeight="1">
-      <c r="B27" s="72" t="s">
+      <c r="B27" s="87" t="s">
         <v>62</v>
       </c>
-      <c r="C27" s="73"/>
+      <c r="C27" s="88"/>
     </row>
     <row r="28" spans="2:13" ht="15" customHeight="1">
-      <c r="B28" s="62" t="s">
+      <c r="B28" s="77" t="s">
         <v>63</v>
       </c>
-      <c r="C28" s="63"/>
+      <c r="C28" s="78"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="K5:M18">
@@ -12122,16 +11974,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1">
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="60" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="41"/>
+      <c r="C2" s="61"/>
     </row>
     <row r="3" spans="2:3" ht="19.5" customHeight="1">
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="66" t="s">
         <v>65</v>
       </c>
-      <c r="C3" s="32"/>
+      <c r="C3" s="52"/>
     </row>
     <row r="5" spans="2:3" ht="19.5" customHeight="1">
       <c r="B5" s="6" t="s">
@@ -12308,6 +12160,6 @@
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/산출물/04_3일차_팀프로젝트_실습기획서_템플렛.xlsx
+++ b/산출물/04_3일차_팀프로젝트_실습기획서_템플렛.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAFY\Desktop\안재윤\localhub\산출물\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE06840-C727-44EC-BCBA-F8A8A45ACB02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3493736E-B567-4110-96EA-3A6E61F959B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_사용안내" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="254">
   <si>
     <t>실습 소재</t>
   </si>
@@ -8402,9 +8402,6 @@
     <t>팀전체</t>
   </si>
   <si>
-    <t>FE</t>
-  </si>
-  <si>
     <t>제공 JSON 데이터 연동 및 리스트 UI 구현</t>
   </si>
   <si>
@@ -8414,9 +8411,6 @@
     <t>OpenAI API 연동 및 챗봇 컴포넌트 개발</t>
   </si>
   <si>
-    <t>선택 기능(날씨 API, 게시판 검색) 구현</t>
-  </si>
-  <si>
     <t>Netlify 환경 설정 및 빌드 배포</t>
   </si>
   <si>
@@ -8438,9 +8432,6 @@
     <t>2026-07-16</t>
   </si>
   <si>
-    <t>예정</t>
-  </si>
-  <si>
     <t>완료</t>
   </si>
   <si>
@@ -8826,6 +8817,49 @@
       </rPr>
       <t>추가</t>
     </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>목록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 기능 - 상세 정보를 카테고리 별로 분류</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>마커 상세 팝업 윈도우 - 지도의 마커를 클릭하면 상세 정보 윈도우가 팝업</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>실시간 마커 동기화 - 메뉴에서 카테고리를 클릭하면 지도 위에 전용 마커가 시각화</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>축제공연행사 검색 기능 - 기간을 설정하면 해당하는 축제공연행사 마커 노출</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>검색 기반 마커 필터링 - 검색창에 키워드 입력하면 검색돤 컨텐츠 관련 마커들만 지도에 노출</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>선택 기능 구현</t>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
 </sst>
@@ -8836,7 +8870,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="&quot;Day &quot;0"/>
   </numFmts>
-  <fonts count="49">
+  <fonts count="51">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9181,8 +9215,22 @@
       <name val="Noto Sans CJK SC"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF222222"/>
+      <name val="돋움"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="21">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -9301,6 +9349,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFD0E0E3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -9460,7 +9520,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -9598,6 +9658,13 @@
     <xf numFmtId="0" fontId="47" fillId="20" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -9653,6 +9720,15 @@
     <xf numFmtId="0" fontId="41" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -9665,14 +9741,29 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -9710,35 +9801,29 @@
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="44" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -10056,10 +10141,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="31.5" customHeight="1">
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="58" t="s">
         <v>108</v>
       </c>
-      <c r="C2" s="55"/>
+      <c r="C2" s="58"/>
     </row>
     <row r="4" spans="2:3" ht="19.5" customHeight="1">
       <c r="B4" s="14" t="s">
@@ -10094,10 +10179,10 @@
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="54" t="s">
         <v>114</v>
       </c>
-      <c r="C9" s="52"/>
+      <c r="C9" s="55"/>
     </row>
     <row r="10" spans="2:3" ht="27">
       <c r="B10" s="4" t="s">
@@ -10148,28 +10233,28 @@
       </c>
     </row>
     <row r="17" spans="2:3" ht="15" customHeight="1">
-      <c r="B17" s="53" t="s">
+      <c r="B17" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="54"/>
+      <c r="C17" s="57"/>
     </row>
     <row r="18" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B18" s="56" t="s">
+      <c r="B18" s="59" t="s">
         <v>125</v>
       </c>
-      <c r="C18" s="57"/>
+      <c r="C18" s="60"/>
     </row>
     <row r="19" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B19" s="49" t="s">
+      <c r="B19" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="50"/>
+      <c r="C19" s="53"/>
     </row>
     <row r="20" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B20" s="49" t="s">
+      <c r="B20" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="50"/>
+      <c r="C20" s="53"/>
     </row>
     <row r="21" spans="2:3" ht="27.75" customHeight="1"/>
   </sheetData>
@@ -10203,13 +10288,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="30" customHeight="1">
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
     </row>
     <row r="4" spans="2:10" ht="19.5" customHeight="1">
       <c r="B4" s="6" t="s">
@@ -10301,46 +10386,46 @@
     </row>
     <row r="9" spans="2:10" ht="14.1" customHeight="1"/>
     <row r="10" spans="2:10" ht="15" customHeight="1">
-      <c r="B10" s="62" t="s">
+      <c r="B10" s="65" t="s">
         <v>126</v>
       </c>
-      <c r="C10" s="59"/>
-      <c r="D10" s="59"/>
-      <c r="E10" s="59"/>
-      <c r="F10" s="52"/>
+      <c r="C10" s="62"/>
+      <c r="D10" s="62"/>
+      <c r="E10" s="62"/>
+      <c r="F10" s="55"/>
     </row>
     <row r="11" spans="2:10" ht="24" customHeight="1">
       <c r="B11" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" s="61" t="s">
         <v>127</v>
       </c>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
+      <c r="D11" s="62"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
     </row>
     <row r="12" spans="2:10" ht="24" customHeight="1">
       <c r="B12" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="58" t="s">
+      <c r="C12" s="61" t="s">
         <v>128</v>
       </c>
-      <c r="D12" s="59"/>
-      <c r="E12" s="59"/>
-      <c r="F12" s="59"/>
+      <c r="D12" s="62"/>
+      <c r="E12" s="62"/>
+      <c r="F12" s="62"/>
     </row>
     <row r="13" spans="2:10" ht="24" customHeight="1">
       <c r="B13" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="58" t="s">
+      <c r="C13" s="61" t="s">
         <v>129</v>
       </c>
-      <c r="D13" s="59"/>
-      <c r="E13" s="59"/>
-      <c r="F13" s="59"/>
+      <c r="D13" s="62"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -10369,10 +10454,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="31.5" customHeight="1">
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="58" t="s">
         <v>108</v>
       </c>
-      <c r="C2" s="55"/>
+      <c r="C2" s="58"/>
     </row>
     <row r="4" spans="2:3" ht="19.5" customHeight="1">
       <c r="B4" s="14" t="s">
@@ -10407,10 +10492,10 @@
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="54" t="s">
         <v>114</v>
       </c>
-      <c r="C9" s="52"/>
+      <c r="C9" s="55"/>
     </row>
     <row r="10" spans="2:3" ht="27">
       <c r="B10" s="4" t="s">
@@ -10461,28 +10546,28 @@
       </c>
     </row>
     <row r="17" spans="2:3" ht="15" customHeight="1">
-      <c r="B17" s="53" t="s">
+      <c r="B17" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="54"/>
+      <c r="C17" s="57"/>
     </row>
     <row r="18" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B18" s="56" t="s">
+      <c r="B18" s="59" t="s">
         <v>125</v>
       </c>
-      <c r="C18" s="57"/>
+      <c r="C18" s="60"/>
     </row>
     <row r="19" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B19" s="49" t="s">
+      <c r="B19" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="50"/>
+      <c r="C19" s="53"/>
     </row>
     <row r="20" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B20" s="49" t="s">
+      <c r="B20" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="50"/>
+      <c r="C20" s="53"/>
     </row>
     <row r="21" spans="2:3" ht="27.75" customHeight="1"/>
   </sheetData>
@@ -10517,22 +10602,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="30" customHeight="1">
-      <c r="B2" s="63" t="s">
+      <c r="B2" s="66" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
     </row>
     <row r="3" spans="2:6" ht="28.35" customHeight="1">
-      <c r="B3" s="64" t="s">
+      <c r="B3" s="67" t="s">
         <v>138</v>
       </c>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="52"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="55"/>
     </row>
     <row r="4" spans="2:6" ht="35.65" customHeight="1">
       <c r="B4" s="8" t="s">
@@ -10562,61 +10647,61 @@
     </row>
     <row r="6" spans="2:6" ht="30" customHeight="1">
       <c r="B6" s="44" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E6" s="45" t="s">
         <v>148</v>
       </c>
       <c r="F6" s="46" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="30" customHeight="1">
       <c r="B7" s="44" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D7" s="46" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E7" s="45" t="s">
         <v>149</v>
       </c>
       <c r="F7" s="46" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="30" customHeight="1">
       <c r="B8" s="44" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C8" s="45" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D8" s="46" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E8" s="45" t="s">
         <v>150</v>
       </c>
       <c r="F8" s="46" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="30" customHeight="1">
       <c r="B9" s="44" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C9" s="45" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D9" s="46" t="s">
         <v>151</v>
@@ -10625,15 +10710,15 @@
         <v>152</v>
       </c>
       <c r="F9" s="46" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="30" customHeight="1">
       <c r="B10" s="44" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C10" s="45" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D10" s="46" t="s">
         <v>153</v>
@@ -10647,10 +10732,10 @@
     </row>
     <row r="11" spans="2:6" ht="30" customHeight="1">
       <c r="B11" s="47" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C11" s="45" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D11" s="46" t="s">
         <v>156</v>
@@ -10659,15 +10744,15 @@
         <v>157</v>
       </c>
       <c r="F11" s="46" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="12" spans="2:6" ht="30" customHeight="1">
       <c r="B12" s="47" t="s">
+        <v>236</v>
+      </c>
+      <c r="C12" s="45" t="s">
         <v>239</v>
-      </c>
-      <c r="C12" s="45" t="s">
-        <v>242</v>
       </c>
       <c r="D12" s="46" t="s">
         <v>158</v>
@@ -10681,10 +10766,10 @@
     </row>
     <row r="13" spans="2:6" ht="30" customHeight="1">
       <c r="B13" s="47" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C13" s="45" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D13" s="46" t="s">
         <v>161</v>
@@ -10693,15 +10778,15 @@
         <v>162</v>
       </c>
       <c r="F13" s="46" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="30" customHeight="1">
       <c r="B14" s="47" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C14" s="45" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D14" s="46" t="s">
         <v>163</v>
@@ -10710,15 +10795,15 @@
         <v>164</v>
       </c>
       <c r="F14" s="46" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="30" customHeight="1">
       <c r="B15" s="48" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C15" s="45" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D15" s="46" t="s">
         <v>165</v>
@@ -10820,37 +10905,37 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="30" customHeight="1">
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
     </row>
     <row r="3" spans="2:8" ht="72.400000000000006" customHeight="1">
-      <c r="B3" s="65" t="s">
+      <c r="B3" s="68" t="s">
         <v>132</v>
       </c>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="52"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="55"/>
     </row>
     <row r="4" spans="2:8" ht="18" customHeight="1">
-      <c r="B4" s="66" t="s">
+      <c r="B4" s="69" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="59"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="52"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="55"/>
     </row>
     <row r="5" spans="2:8" ht="31.5" customHeight="1">
       <c r="B5" s="10" t="s">
@@ -10967,7 +11052,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="107" t="s">
         <v>189</v>
       </c>
     </row>
@@ -11088,7 +11173,7 @@
         <v>40</v>
       </c>
       <c r="H14" s="32" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="47.25" customHeight="1">
@@ -11143,14 +11228,14 @@
       <c r="B18" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="C18" s="67" t="s">
+      <c r="C18" s="70" t="s">
         <v>202</v>
       </c>
-      <c r="D18" s="68"/>
-      <c r="E18" s="68"/>
-      <c r="F18" s="68"/>
-      <c r="G18" s="68"/>
-      <c r="H18" s="69"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="71"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -11200,7 +11285,7 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="B2:C23"/>
+  <dimension ref="B2:C29"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -11210,16 +11295,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1">
-      <c r="B2" s="63" t="s">
+      <c r="B2" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="61"/>
+      <c r="C2" s="64"/>
     </row>
     <row r="3" spans="2:3" ht="18" customHeight="1">
-      <c r="B3" s="76" t="s">
+      <c r="B3" s="75" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="52"/>
+      <c r="C3" s="55"/>
     </row>
     <row r="4" spans="2:3" ht="30" customHeight="1">
       <c r="B4" s="1" t="s">
@@ -11254,104 +11339,143 @@
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="74" t="s">
+      <c r="B9" s="73" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="75"/>
+      <c r="C9" s="74"/>
     </row>
     <row r="10" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B10" s="49" t="s">
+      <c r="B10" s="52" t="s">
         <v>195</v>
       </c>
-      <c r="C10" s="50"/>
+      <c r="C10" s="53"/>
     </row>
     <row r="11" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B11" s="49" t="s">
+      <c r="B11" s="52" t="s">
         <v>196</v>
       </c>
-      <c r="C11" s="50"/>
+      <c r="C11" s="53"/>
     </row>
     <row r="12" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B12" s="56" t="s">
+      <c r="B12" s="59" t="s">
         <v>197</v>
       </c>
-      <c r="C12" s="57"/>
+      <c r="C12" s="60"/>
     </row>
     <row r="13" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B13" s="56" t="s">
+      <c r="B13" s="59" t="s">
         <v>198</v>
       </c>
-      <c r="C13" s="57"/>
+      <c r="C13" s="60"/>
     </row>
     <row r="14" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B14" s="49" t="s">
+      <c r="B14" s="52" t="s">
         <v>199</v>
       </c>
-      <c r="C14" s="50"/>
+      <c r="C14" s="53"/>
     </row>
     <row r="15" spans="2:3">
-      <c r="B15" s="58" t="s">
+      <c r="B15" s="61" t="s">
+        <v>246</v>
+      </c>
+      <c r="C15" s="53"/>
+    </row>
+    <row r="16" spans="2:3" s="29" customFormat="1">
+      <c r="B16" s="50"/>
+      <c r="C16" s="51"/>
+    </row>
+    <row r="17" spans="2:3" ht="15" customHeight="1">
+      <c r="B17" s="78" t="s">
+        <v>205</v>
+      </c>
+      <c r="C17" s="79"/>
+    </row>
+    <row r="18" spans="2:3" s="49" customFormat="1" ht="15" customHeight="1">
+      <c r="B18" s="102" t="s">
+        <v>248</v>
+      </c>
+      <c r="C18" s="103"/>
+    </row>
+    <row r="19" spans="2:3" s="49" customFormat="1" ht="15" customHeight="1">
+      <c r="B19" s="104" t="s">
+        <v>251</v>
+      </c>
+      <c r="C19" s="103"/>
+    </row>
+    <row r="20" spans="2:3" s="49" customFormat="1" ht="15" customHeight="1">
+      <c r="B20" s="104" t="s">
+        <v>250</v>
+      </c>
+      <c r="C20" s="103"/>
+    </row>
+    <row r="21" spans="2:3" s="49" customFormat="1" ht="15" customHeight="1">
+      <c r="B21" s="104" t="s">
         <v>249</v>
       </c>
-      <c r="C15" s="50"/>
-    </row>
-    <row r="16" spans="2:3" s="29" customFormat="1">
-      <c r="B16" s="97"/>
-      <c r="C16" s="98"/>
-    </row>
-    <row r="17" spans="2:3" ht="15" customHeight="1">
-      <c r="B17" s="72" t="s">
-        <v>205</v>
-      </c>
-      <c r="C17" s="73"/>
-    </row>
-    <row r="18" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B18" s="58" t="s">
-        <v>250</v>
-      </c>
-      <c r="C18" s="50"/>
-    </row>
-    <row r="20" spans="2:3" ht="15" customHeight="1">
-      <c r="B20" s="70" t="s">
+      <c r="C21" s="103"/>
+    </row>
+    <row r="22" spans="2:3" s="49" customFormat="1" ht="15" customHeight="1">
+      <c r="B22" s="104" t="s">
+        <v>252</v>
+      </c>
+      <c r="C22" s="103"/>
+    </row>
+    <row r="23" spans="2:3" ht="25.5" customHeight="1">
+      <c r="B23" s="61" t="s">
+        <v>247</v>
+      </c>
+      <c r="C23" s="53"/>
+    </row>
+    <row r="24" spans="2:3" s="49" customFormat="1" ht="25.5" customHeight="1">
+      <c r="B24" s="100"/>
+      <c r="C24" s="101"/>
+    </row>
+    <row r="26" spans="2:3" ht="15" customHeight="1">
+      <c r="B26" s="76" t="s">
         <v>206</v>
       </c>
-      <c r="C20" s="71"/>
-    </row>
-    <row r="21" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B21" s="58" t="s">
+      <c r="C26" s="77"/>
+    </row>
+    <row r="27" spans="2:3" ht="25.5" customHeight="1">
+      <c r="B27" s="61" t="s">
         <v>207</v>
       </c>
-      <c r="C21" s="50"/>
-    </row>
-    <row r="22" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B22" s="49" t="s">
+      <c r="C27" s="53"/>
+    </row>
+    <row r="28" spans="2:3" ht="25.5" customHeight="1">
+      <c r="B28" s="52" t="s">
         <v>200</v>
       </c>
-      <c r="C22" s="50"/>
-    </row>
-    <row r="23" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B23" s="58" t="s">
+      <c r="C28" s="53"/>
+    </row>
+    <row r="29" spans="2:3" ht="25.5" customHeight="1">
+      <c r="B29" s="61" t="s">
         <v>201</v>
       </c>
-      <c r="C23" s="50"/>
+      <c r="C29" s="53"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B9:C9"/>
+  <mergeCells count="20">
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B17:C17"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -11382,36 +11506,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="27.75" customHeight="1">
-      <c r="B2" s="90" t="s">
+      <c r="B2" s="81" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="64"/>
+      <c r="M2" s="64"/>
     </row>
     <row r="3" spans="2:13" ht="79.7" customHeight="1">
-      <c r="B3" s="89" t="s">
+      <c r="B3" s="80" t="s">
         <v>133</v>
       </c>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="59"/>
-      <c r="K3" s="59"/>
-      <c r="L3" s="59"/>
-      <c r="M3" s="52"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="62"/>
+      <c r="M3" s="55"/>
     </row>
     <row r="4" spans="2:13" ht="25.5" customHeight="1">
       <c r="B4" s="13" t="s">
@@ -11465,10 +11589,10 @@
         <v>211</v>
       </c>
       <c r="F5" s="43" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G5" s="43" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H5" s="5">
         <f t="shared" ref="H5:H18" si="0">IF(OR(F5="",G5=""),"",G5-F5+1)</f>
@@ -11478,7 +11602,7 @@
         <v>100</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="K5" s="42"/>
       <c r="L5" s="3"/>
@@ -11494,24 +11618,24 @@
       <c r="D6" s="41" t="s">
         <v>209</v>
       </c>
-      <c r="E6" s="40" t="s">
-        <v>212</v>
+      <c r="E6" s="43" t="s">
+        <v>211</v>
       </c>
       <c r="F6" s="43" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G6" s="43" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H6" s="5">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I6" s="5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="K6" s="42"/>
       <c r="L6" s="3"/>
@@ -11527,24 +11651,24 @@
       <c r="D7" s="41" t="s">
         <v>210</v>
       </c>
-      <c r="E7" s="40" t="s">
-        <v>212</v>
+      <c r="E7" s="43" t="s">
+        <v>211</v>
       </c>
       <c r="F7" s="43" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G7" s="43" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H7" s="5">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I7" s="5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="K7" s="42"/>
       <c r="L7" s="3"/>
@@ -11558,26 +11682,26 @@
         <v>58</v>
       </c>
       <c r="D8" s="41" t="s">
-        <v>213</v>
-      </c>
-      <c r="E8" s="40" t="s">
         <v>212</v>
       </c>
+      <c r="E8" s="43" t="s">
+        <v>211</v>
+      </c>
       <c r="F8" s="43" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G8" s="43" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H8" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="I8" s="5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="K8" s="42"/>
       <c r="L8" s="42"/>
@@ -11591,26 +11715,26 @@
         <v>58</v>
       </c>
       <c r="D9" s="41" t="s">
-        <v>214</v>
-      </c>
-      <c r="E9" s="40" t="s">
-        <v>212</v>
+        <v>213</v>
+      </c>
+      <c r="E9" s="43" t="s">
+        <v>211</v>
       </c>
       <c r="F9" s="43" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G9" s="43" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H9" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="I9" s="5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="K9" s="42"/>
       <c r="L9" s="42"/>
@@ -11624,26 +11748,26 @@
         <v>58</v>
       </c>
       <c r="D10" s="41" t="s">
-        <v>215</v>
-      </c>
-      <c r="E10" s="40" t="s">
-        <v>212</v>
+        <v>214</v>
+      </c>
+      <c r="E10" s="43" t="s">
+        <v>211</v>
       </c>
       <c r="F10" s="43" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G10" s="43" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H10" s="5">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I10" s="5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="42"/>
@@ -11657,30 +11781,30 @@
         <v>58</v>
       </c>
       <c r="D11" s="41" t="s">
-        <v>216</v>
-      </c>
-      <c r="E11" s="40" t="s">
-        <v>212</v>
+        <v>253</v>
+      </c>
+      <c r="E11" s="43" t="s">
+        <v>211</v>
       </c>
       <c r="F11" s="43" t="s">
+        <v>220</v>
+      </c>
+      <c r="G11" s="106">
+        <v>46219</v>
+      </c>
+      <c r="H11" s="5">
+        <f>IF(OR(F11="",G11=""),"",G11-F11+1)</f>
+        <v>2</v>
+      </c>
+      <c r="I11" s="5">
+        <v>100</v>
+      </c>
+      <c r="J11" s="5" t="s">
         <v>222</v>
-      </c>
-      <c r="G11" s="43" t="s">
-        <v>222</v>
-      </c>
-      <c r="H11" s="5">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I11" s="5">
-        <v>0</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>224</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="42"/>
-      <c r="M11" s="3"/>
+      <c r="M11" s="42"/>
     </row>
     <row r="12" spans="2:13" ht="30" customHeight="1">
       <c r="B12" s="5">
@@ -11690,30 +11814,30 @@
         <v>59</v>
       </c>
       <c r="D12" s="41" t="s">
-        <v>217</v>
-      </c>
-      <c r="E12" s="40" t="s">
-        <v>212</v>
-      </c>
-      <c r="F12" s="43" t="s">
-        <v>222</v>
-      </c>
-      <c r="G12" s="43" t="s">
-        <v>222</v>
+        <v>215</v>
+      </c>
+      <c r="E12" s="43" t="s">
+        <v>211</v>
+      </c>
+      <c r="F12" s="106">
+        <v>46219</v>
+      </c>
+      <c r="G12" s="106">
+        <v>46219</v>
       </c>
       <c r="H12" s="5">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I12" s="5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="K12" s="3"/>
-      <c r="L12" s="42"/>
-      <c r="M12" s="3"/>
+      <c r="L12" s="105"/>
+      <c r="M12" s="42"/>
     </row>
     <row r="13" spans="2:13" ht="30" customHeight="1">
       <c r="B13" s="5">
@@ -11723,26 +11847,26 @@
         <v>60</v>
       </c>
       <c r="D13" s="41" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E13" s="40" t="s">
         <v>211</v>
       </c>
       <c r="F13" s="43" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G13" s="43" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H13" s="5">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I13" s="5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
@@ -11756,26 +11880,26 @@
         <v>61</v>
       </c>
       <c r="D14" s="41" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E14" s="40" t="s">
         <v>211</v>
       </c>
       <c r="F14" s="43" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G14" s="43" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H14" s="5">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I14" s="5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
@@ -11789,26 +11913,26 @@
         <v>62</v>
       </c>
       <c r="D15" s="41" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E15" s="40" t="s">
         <v>211</v>
       </c>
       <c r="F15" s="43" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G15" s="43" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H15" s="5">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I15" s="5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
@@ -11872,72 +11996,72 @@
       <c r="M18" s="3"/>
     </row>
     <row r="20" spans="2:13" ht="15" customHeight="1">
-      <c r="B20" s="91" t="s">
+      <c r="B20" s="82" t="s">
         <v>134</v>
       </c>
-      <c r="C20" s="92"/>
+      <c r="C20" s="83"/>
     </row>
     <row r="21" spans="2:13" ht="15" customHeight="1">
-      <c r="B21" s="93" t="s">
+      <c r="B21" s="84" t="s">
         <v>56</v>
       </c>
-      <c r="C21" s="94"/>
+      <c r="C21" s="85"/>
     </row>
     <row r="22" spans="2:13" ht="15" customHeight="1">
-      <c r="B22" s="95" t="s">
+      <c r="B22" s="86" t="s">
         <v>57</v>
       </c>
-      <c r="C22" s="96"/>
+      <c r="C22" s="87"/>
     </row>
     <row r="23" spans="2:13" ht="15" customHeight="1">
-      <c r="B23" s="79" t="s">
+      <c r="B23" s="90" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="80"/>
+      <c r="C23" s="91"/>
     </row>
     <row r="24" spans="2:13" ht="15" customHeight="1">
-      <c r="B24" s="81" t="s">
+      <c r="B24" s="92" t="s">
         <v>59</v>
       </c>
-      <c r="C24" s="82"/>
+      <c r="C24" s="93"/>
     </row>
     <row r="25" spans="2:13" ht="15" customHeight="1">
-      <c r="B25" s="83" t="s">
+      <c r="B25" s="94" t="s">
         <v>60</v>
       </c>
-      <c r="C25" s="84"/>
+      <c r="C25" s="95"/>
     </row>
     <row r="26" spans="2:13" ht="15" customHeight="1">
-      <c r="B26" s="85" t="s">
+      <c r="B26" s="96" t="s">
         <v>61</v>
       </c>
-      <c r="C26" s="86"/>
+      <c r="C26" s="97"/>
     </row>
     <row r="27" spans="2:13" ht="15" customHeight="1">
-      <c r="B27" s="87" t="s">
+      <c r="B27" s="98" t="s">
         <v>62</v>
       </c>
-      <c r="C27" s="88"/>
+      <c r="C27" s="99"/>
     </row>
     <row r="28" spans="2:13" ht="15" customHeight="1">
-      <c r="B28" s="77" t="s">
+      <c r="B28" s="88" t="s">
         <v>63</v>
       </c>
-      <c r="C28" s="78"/>
+      <c r="C28" s="89"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="K5:M18">
@@ -11974,16 +12098,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1">
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="61"/>
+      <c r="C2" s="64"/>
     </row>
     <row r="3" spans="2:3" ht="19.5" customHeight="1">
-      <c r="B3" s="66" t="s">
+      <c r="B3" s="69" t="s">
         <v>65</v>
       </c>
-      <c r="C3" s="52"/>
+      <c r="C3" s="55"/>
     </row>
     <row r="5" spans="2:3" ht="19.5" customHeight="1">
       <c r="B5" s="6" t="s">
